--- a/ルート・コントローラー仕様書.xlsx
+++ b/ルート・コントローラー仕様書.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>セッションを破棄してログアウトする</t>
+          <t>セッションを破棄してログアウトし、ログインページ(/login)へリダイレクトする</t>
         </is>
       </c>
     </row>

--- a/ルート・コントローラー仕様書.xlsx
+++ b/ルート・コントローラー仕様書.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/ または /books</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>指定ジャンルに紐づく書籍一覧を10件/ページでページネーション表示する</t>
+          <t>指定ジャンルに紐づく書籍一覧を、登録日時の新しい順（同じ日時の場合はIDの新しい順）に10件/ページでページネーション表示する。クエリパラメータfrom（genres / reports）で遷移元を受け取り、「戻る」リンクの遷移先をジャンル一覧またはマイ読書レポートに切り替える（未指定時はジャンル一覧）</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>ログインユーザーがお気に入り登録した書籍一覧を10件/ページでページネーション表示する</t>
+          <t>ログインユーザーがお気に入り登録した書籍一覧を、お気に入りに登録した日時の新しい順に10件/ページでページネーション表示する</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>ログインユーザー自身の通知一覧を新しい順に表示する(★応用機能)</t>
+          <t>ログインユーザー自身の通知一覧を表示する。並び順は第1に作成日時の新しい順、作成日時が同じ場合は第2に「期日3日前（予告）→期日当日（最終警告）→期日3日後（再エンゲージメント）」の順(★応用機能)</t>
         </is>
       </c>
     </row>

--- a/ルート・コントローラー仕様書.xlsx
+++ b/ルート・コントローラー仕様書.xlsx
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>ジャンルを削除する。事前に$genre-&gt;books()-&gt;exists()で書籍への紐づきを確認し、紐づきがある場合はエラーメッセージを表示して削除を中止する(DB側のrestrictOnDeleteは保険的な制約)</t>
+          <t>ジャンルを削除する。事前に$genre-&gt;books()-&gt;exists()で書籍への紐づきを確認し、紐づきがある場合はエラーメッセージを表示して削除を中止する(book_genre.genre_idの外部キーは削除時CASCADEのため、DB側では削除を拒否しない)</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>指定書籍にレビューを投稿する。ReviewPolicy::createで1書籍1回に制限</t>
+          <t>指定書籍にレビューを投稿する。ReviewPolicy::createで1書籍1回に制限(ReviewRequest::authorize()で入力チェックより先に判定)</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>評価・コメントを更新する</t>
+          <t>評価・コメントを更新する。ReviewPolicy::updateで投稿者本人か確認(ReviewRequest::authorize()で入力チェックより先に判定)</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>入力内容をバリデーションし、読書計画を作成する。ReadingPlanPolicy::createで同一書籍の進行中計画の重複を防止(★応用機能)</t>
+          <t>入力内容をバリデーションし、読書計画を作成する。ReadingPlanPolicy::createで同一書籍の進行中計画の重複を防止(ReadingPlanRequest::authorize()で入力チェックより先に判定)(★応用機能)</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>期日を変更する。更新後のステータスは必ず「進行中」に戻る(★応用機能)</t>
+          <t>期日を変更する。ReadingPlanPolicy::updateで本人かつ更新可能な状態か確認(ReadingPlanRequest::authorize()で入力チェックより先に判定)。更新後のステータスは必ず「進行中」に戻る(★応用機能)</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>計画を削除する。関連する通知の削除とあわせて1つのDBトランザクションで実行(★応用機能)</t>
+          <t>計画を削除する。計画に紐づくリマインダー通知の削除と計画の削除を、コントローラー内で1つのDBトランザクションとして実行(★応用機能)</t>
         </is>
       </c>
     </row>

--- a/ルート・コントローラー仕様書.xlsx
+++ b/ルート・コントローラー仕様書.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>書籍を削除する。関連するレビュー・お気に入り・ジャンル紐づけはcascadeで削除</t>
+          <t>書籍を削除する。関連するレビュー・お気に入り・ジャンル紐づけ・読書計画はcascadeで削除(読書計画に紐づくリマインダー通知は削除しない。コーチ確認済み)</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>★API書籍一覧取得</t>
+          <t>AP01:書籍一覧API</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>キーワード検索・ジャンル絞り込み・ページネーションに対応。各書籍にジャンル情報・平均評価・レビュー件数を含めてBookResourceで整形して返す(★応用機能)</t>
+          <t>キーワード検索・ジャンル絞り込み・ページネーション(1ページ10件固定。件数はクライアントから指定できず、次のページはpageを指定して再取得)に対応。各書籍にジャンル情報・平均評価・レビュー件数を含めてBookResourceで整形して返す</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>★API書籍詳細取得</t>
+          <t>AP02:書籍詳細API</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>★API書籍登録</t>
+          <t>AP03:書籍登録API</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Sanctumトークン認証が必須。登録者ID(user_id)はリクエストではなくAuth::id()から設定する。登録成功時は201</t>
+          <t>Sanctumトークン認証が必須。登録者ID(user_id)はリクエストではなくAuth::id()から設定する。登録成功時は201。認証・認可は★AP06:SanctumAPIトークン認証(応用)</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>★API書籍更新</t>
+          <t>AP04:書籍更新API</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Sanctum認証に加え、BookPolicy::updateで書籍の所有者本人のみ更新できる</t>
+          <t>Sanctum認証に加え、BookPolicy::updateで書籍の所有者本人のみ更新できる。認証・認可は★AP06:SanctumAPIトークン認証(応用)</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>★API書籍削除</t>
+          <t>AP05:書籍削除API</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2222,7 +2222,47 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Sanctum認証に加え、BookPolicy::deleteで書籍の所有者本人のみ削除できる。削除成功時は204</t>
+          <t>Sanctum認証に加え、BookPolicy::deleteで書籍の所有者本人のみ削除できる。削除成功時は204。認証・認可は★AP06:SanctumAPIトークン認証(応用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>（Laravel標準）ログインユーザー情報取得</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>/api/user</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>クロージャ(routes/api.php)</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>必要(Sanctum)</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Laravel標準で routes/api.php に定義されているルート（Sanctumトークン認証が必要。$request-&gt;user() を返す）。本アプリの画面・機能からは使用しておらず、テストの対象外</t>
         </is>
       </c>
     </row>
